--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון הולצמן לראות אותך הלילה</v>
+        <v>אוליביה רודריגו Drop Dead</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9c%d7%a8%d7%90%d7%95%d7%aa-%d7%90%d7%95%d7%aa%d7%9a-%d7%94%d7%9c%d7%99%d7%9c%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%a8%d7%95%d7%93%d7%a8%d7%99%d7%92%d7%95-drop-dead/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"לראות אותך הלילה" של שרון הולצמן הוא בלדת רוק אינטימית – כזו שלא נשענת על תחכום צורני אלא על רגש חשוף וישיר. דווקא הפשטות היא חלק מרכזי מהכוח שלה. כבר בשורה הפותחת נוצרת דינמיקה של תלות רגשית חזקה – "רק</v>
+        <v>“לילה אחד השתעממתי במיטה / ועקבתי אחריך באינטרנט,” שרה אוליביה רודריגו בסינגל הקאמבק שלה, שכובש כל פסגה במצעדי העולם. שירים חדים, אובססיביים ובלתי מתפשרים על רומנטיקה – תמיד עם מודעות עצמית לעוצמה שלהם, או קריצה לאופן שבו בנות מאוהבות מתויגות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון הולצמן לראות אותך הלילה</v>
+        <v>אוליביה רודריגו Drop Dead</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אוליביה רודריגו Drop Dead</v>
+        <v>אריאל דימנט – כשאתה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%a8%d7%95%d7%93%d7%a8%d7%99%d7%92%d7%95-drop-dead/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%90%d7%9c-%d7%93%d7%99%d7%9e%d7%a0%d7%98-%d7%9b%d7%a9%d7%90%d7%aa%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“לילה אחד השתעממתי במיטה / ועקבתי אחריך באינטרנט,” שרה אוליביה רודריגו בסינגל הקאמבק שלה, שכובש כל פסגה במצעדי העולם. שירים חדים, אובססיביים ובלתי מתפשרים על רומנטיקה – תמיד עם מודעות עצמית לעוצמה שלהם, או קריצה לאופן שבו בנות מאוהבות מתויגות</v>
+        <v>הקאבר ל־“כשאתה” בביצועה של אריאל דימנט מתוך המחזמר "בגלל הרוח" משירי שלומי שבת, הוא דוגמה יפה לאיך שיר אהבה מוכר יכול לקבל משמעות חדשה לגמרי כשהוא נכנס להקשר דרמטי. במקור, השיר של שלומי שבת בדואט עם בתו מנור שבת הוא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אוליביה רודריגו Drop Dead</v>
+        <v>אריאל דימנט – כשאתה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>הפטריקים – מלאך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%9e%d7%9c%d7%90%d7%9a/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>“מלאך” של מאיר גולדברג ודודי לוי בביצוע  הפטריקים (דודי לוי + אבטיפוס) הוא טקסט טעון בדימויים פואטיים שמערבבים בין פנטזיה קוסמית לבין חוויה מאוד אנושית של אובדן, זיכרון וזהות. המלאך מתואר כיצור חופש שמביט מלמעלה, אך החופש הזה מתגלה כאשליה:</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>הפטריקים – מלאך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריאל דימנט – כשאתה</v>
+        <v>יובל לוי – החיה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%90%d7%9c-%d7%93%d7%99%d7%9e%d7%a0%d7%98-%d7%9b%d7%a9%d7%90%d7%aa%d7%94/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%9c%d7%95%d7%99-%d7%94%d7%97%d7%99%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר ל־“כשאתה” בביצועה של אריאל דימנט מתוך המחזמר "בגלל הרוח" משירי שלומי שבת, הוא דוגמה יפה לאיך שיר אהבה מוכר יכול לקבל משמעות חדשה לגמרי כשהוא נכנס להקשר דרמטי. במקור, השיר של שלומי שבת בדואט עם בתו מנור שבת הוא</v>
+        <v>יובל לוי שרה שיר פופ שנשמע קליל וכיפי על יחסים בינה ובינו, אבל מתחת לפני השטח מסתתרת בו התפכחות לא פשוטה המציגה את הפער בין מה שדמיינת למה שהיה באמת הפתיחה: “אתה היית החיה שלי / הייתי היפה שלך” מייצרת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריאל דימנט – כשאתה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>הפטריקים – מלאך</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%9e%d7%9c%d7%90%d7%9a/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>“מלאך” של מאיר גולדברג ודודי לוי בביצוע  הפטריקים (דודי לוי + אבטיפוס) הוא טקסט טעון בדימויים פואטיים שמערבבים בין פנטזיה קוסמית לבין חוויה מאוד אנושית של אובדן, זיכרון וזהות. המלאך מתואר כיצור חופש שמביט מלמעלה, אך החופש הזה מתגלה כאשליה:</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>הפטריקים – מלאך</v>
+        <v>יובל לוי – החיה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל לוי – החיה</v>
+        <v>נינט – כחול לבן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%9c%d7%95%d7%99-%d7%94%d7%97%d7%99%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%9b%d7%97%d7%95%d7%9c-%d7%9c%d7%91%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל לוי שרה שיר פופ שנשמע קליל וכיפי על יחסים בינה ובינו, אבל מתחת לפני השטח מסתתרת בו התפכחות לא פשוטה המציגה את הפער בין מה שדמיינת למה שהיה באמת הפתיחה: “אתה היית החיה שלי / הייתי היפה שלך” מייצרת</v>
+        <v>השיר “כחול לבן” של נינט טייב הוא אחד השירים הפחות שגרתיים בפופ הישראלי – מין קולאז’ מוזיקלי שמערב הומור, נוסטלגיה, ביקורת תרבותית והצהרה אישית. זה שיר שלא מנסה להיות “יפה” במובן הקלאסי, אלא לשחק עם זהויות וסגנונות. הדבר הכי בולט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל לוי – החיה</v>
+        <v>נינט – כחול לבן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נינט – כחול לבן</v>
+        <v>דנה ברגר – אם נותרנו נאהב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%9b%d7%97%d7%95%d7%9c-%d7%9c%d7%91%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%94-%d7%91%d7%a8%d7%92%d7%a8-%d7%90%d7%9d-%d7%a0%d7%95%d7%aa%d7%a8%d7%a0%d7%95-%d7%a0%d7%90%d7%94%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “כחול לבן” של נינט טייב הוא אחד השירים הפחות שגרתיים בפופ הישראלי – מין קולאז’ מוזיקלי שמערב הומור, נוסטלגיה, ביקורת תרבותית והצהרה אישית. זה שיר שלא מנסה להיות “יפה” במובן הקלאסי, אלא לשחק עם זהויות וסגנונות. הדבר הכי בולט</v>
+        <v>דנה ברגר שרה אמירה כמעט אידיאולוגית  מבלי להכביד. המסר: חיים עד הסוף, כאן ועכשיו למרות הכל  הטקסט יכול להתפרש גם כברירת מחדל, אבל בכיוון חיובי יותר הוא בנוי סביב בחירות – אם כבר עושים משהו – אז עד הסוף, אם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נינט – כחול לבן</v>
+        <v>דנה ברגר – אם נותרנו נאהב</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אבי אבורומי – קח אותי לתאילנד</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%99-%d7%90%d7%91%d7%95%d7%a8%d7%95%d7%9e%d7%99-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%aa%d7%90%d7%99%d7%9c%d7%a0%d7%93/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>להיט  שנבנה קודם כל כדי לעבוד מהר לתפוס באז בהאזנה ראשונה, להיכנס לפלייליסטים, ולייצר תחושת בריחה מיידית. בבסיס השיר עומד רעיון מאוד ברור: עייפות מהשגרה רצון להתנתק מדרמות, מלחמות ולחצים, לממש פנטזיה של חופש מוחלט במקום אקזוטי (תאילנד) תאילנד כאן</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אבי אבורומי – קח אותי לתאילנד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דנה ברגר – אם נותרנו נאהב</v>
+        <v>שרית חדד – המזרח הרחוק</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%94-%d7%91%d7%a8%d7%92%d7%a8-%d7%90%d7%9d-%d7%a0%d7%95%d7%aa%d7%a8%d7%a0%d7%95-%d7%a0%d7%90%d7%94%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%99%d7%aa-%d7%97%d7%93%d7%93-%d7%94%d7%9e%d7%96%d7%a8%d7%97-%d7%94%d7%a8%d7%97%d7%95%d7%a7/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דנה ברגר שרה אמירה כמעט אידיאולוגית  מבלי להכביד. המסר: חיים עד הסוף, כאן ועכשיו למרות הכל  הטקסט יכול להתפרש גם כברירת מחדל, אבל בכיוון חיובי יותר הוא בנוי סביב בחירות – אם כבר עושים משהו – אז עד הסוף, אם</v>
+        <v>“המזרח הרחוק” ששרה שרית חדד הוא  פופ ים־תיכוני מלודי, זורם, נעים לאוזן  בקצב מיד-טמפו, מלודיה קליטה שמתפתחת בצורה חלקה, הפקה נקייה, כמעט “רדיו-פרנדלי” מושלמת.  שיר שנשמע כאילו נועד לנסיעה ארוכה, רדיו ברקע, האזנה כיפית. השורה “כמעט כל רמזור בעיר הפך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דנה ברגר – אם נותרנו נאהב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אבי אבורומי – קח אותי לתאילנד</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%99-%d7%90%d7%91%d7%95%d7%a8%d7%95%d7%9e%d7%99-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%aa%d7%90%d7%99%d7%9c%d7%a0%d7%93/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>להיט  שנבנה קודם כל כדי לעבוד מהר לתפוס באז בהאזנה ראשונה, להיכנס לפלייליסטים, ולייצר תחושת בריחה מיידית. בבסיס השיר עומד רעיון מאוד ברור: עייפות מהשגרה רצון להתנתק מדרמות, מלחמות ולחצים, לממש פנטזיה של חופש מוחלט במקום אקזוטי (תאילנד) תאילנד כאן</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אבי אבורומי – קח אותי לתאילנד</v>
+        <v>שרית חדד – המזרח הרחוק</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרית חדד – המזרח הרחוק</v>
+        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%99%d7%aa-%d7%97%d7%93%d7%93-%d7%94%d7%9e%d7%96%d7%a8%d7%97-%d7%94%d7%a8%d7%97%d7%95%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%9c-%d7%95%d7%99%d7%99%d7%9f-%d7%a0%d7%95%d7%a4%d7%99%d7%94-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%90%d7%99%d7%a9%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-06</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“המזרח הרחוק” ששרה שרית חדד הוא  פופ ים־תיכוני מלודי, זורם, נעים לאוזן  בקצב מיד-טמפו, מלודיה קליטה שמתפתחת בצורה חלקה, הפקה נקייה, כמעט “רדיו-פרנדלי” מושלמת.  שיר שנשמע כאילו נועד לנסיעה ארוכה, רדיו ברקע, האזנה כיפית. השורה “כמעט כל רמזור בעיר הפך</v>
+        <v>השיר “להרגיש אישה” ששרה נופיה הוא בלדה דרמטית שמנסה לתפוס רגע רגשי מאוד ספציפי – קשר קצר, עוצמתי, כמעט משקם,  ואז את ההתפרקות שלו. השיר נוגע בחוויה של אהבה לא יציבה, מהירה, ושברירית. השיר בנוי כמו סיפור כרונולוגי: מפגש אקראי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרית חדד – המזרח הרחוק</v>
+        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
+        <v>דיקלה – חולה מאהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%9c-%d7%95%d7%99%d7%99%d7%9f-%d7%a0%d7%95%d7%a4%d7%99%d7%94-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%90%d7%99%d7%a9%d7%94/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%a7%d7%9c%d7%94-%d7%97%d7%95%d7%9c%d7%94-%d7%9e%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “להרגיש אישה” ששרה נופיה הוא בלדה דרמטית שמנסה לתפוס רגע רגשי מאוד ספציפי – קשר קצר, עוצמתי, כמעט משקם,  ואז את ההתפרקות שלו. השיר נוגע בחוויה של אהבה לא יציבה, מהירה, ושברירית. השיר בנוי כמו סיפור כרונולוגי: מפגש אקראי</v>
+        <v>דיקלה שרה בלדת פופ־מזרחית שמצליחה להפוך כאב זוגי מוכר למשהו כמעט פיזי. זה שיר שנשען פחות על תחכום ויותר על רגש חשוף. המילים “יש לי דירה ואין לי בית” הן המפתח לשיר. זו שורה פשוטה יחסית, אבל מאוד אפקטיבית: יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>גיל ויין &amp; נופיה – להרגיש אישה</v>
+        <v>דיקלה – חולה מאהבה</v>
       </c>
     </row>
   </sheetData>
